--- a/backend/templates/alphabrothers.xlsx
+++ b/backend/templates/alphabrothers.xlsx
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">FGI!$A$1:$AD$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">견적서!$A$1:$AD$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">견적서!$A$1:$AD$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">기술성테스트!$A$1:$AD$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">사용성테스트!$A$1:$AD$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">시장성테스트!$A$1:$AD$47</definedName>
@@ -10188,7 +10188,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD59"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="30" width="5.69921875" customWidth="1"/>
@@ -10548,7 +10548,7 @@
       <c r="E10" s="64"/>
       <c r="F10" s="65"/>
       <c r="G10" s="75">
-        <f>SUM(E18,T18)</f>
+        <f>SUM(E23,T23)</f>
         <v>55000000</v>
       </c>
       <c r="H10" s="76"/>
@@ -10877,342 +10877,401 @@
       <c r="Y17" s="41"/>
       <c r="Z17" s="42"/>
       <c r="AA17" s="43">
-        <f t="shared" ref="AA17" si="0">SUM(V17*X17)</f>
+        <f>SUM(V17*X17)</f>
         <v>15000000</v>
       </c>
       <c r="AB17" s="41"/>
       <c r="AC17" s="41"/>
       <c r="AD17" s="41"/>
     </row>
-    <row r="18" spans="1:30" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="52" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="53">
-        <f>SUM(T18*0.1)</f>
+    <row r="18" spans="1:30" ht="150" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="58"/>
+      <c r="E18" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="48">
+        <v>5</v>
+      </c>
+      <c r="U18" s="49"/>
+      <c r="V18" s="50">
+        <v>5</v>
+      </c>
+      <c r="W18" s="51"/>
+      <c r="X18" s="41">
+        <v>1000000</v>
+      </c>
+      <c r="Y18" s="41"/>
+      <c r="Z18" s="42"/>
+      <c r="AA18" s="43">
+        <f>SUM(V18*X18)</f>
         <v>5000000</v>
       </c>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q18" s="54"/>
-      <c r="R18" s="54"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="55">
-        <f>SUM(AA13:AD17)</f>
-        <v>50000000</v>
-      </c>
-      <c r="U18" s="56"/>
-      <c r="V18" s="56"/>
-      <c r="W18" s="56"/>
-      <c r="X18" s="56"/>
-      <c r="Y18" s="56"/>
-      <c r="Z18" s="56"/>
-      <c r="AA18" s="56"/>
-      <c r="AB18" s="56"/>
-      <c r="AC18" s="56"/>
-      <c r="AD18" s="56"/>
-    </row>
-    <row r="19" spans="1:30" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="32"/>
+      <c r="AB18" s="41"/>
+      <c r="AC18" s="41"/>
+      <c r="AD18" s="41"/>
+    </row>
+    <row r="19" spans="1:30" ht="150" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="59"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="60"/>
       <c r="E19" s="33" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="F19" s="34"/>
       <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="35" t="s">
+      <c r="H19" s="44"/>
+      <c r="I19" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="48">
+        <v>30</v>
+      </c>
+      <c r="U19" s="49"/>
+      <c r="V19" s="50">
+        <v>2</v>
+      </c>
+      <c r="W19" s="51"/>
+      <c r="X19" s="41">
+        <v>5000000</v>
+      </c>
+      <c r="Y19" s="41"/>
+      <c r="Z19" s="42"/>
+      <c r="AA19" s="43">
+        <f>SUM(V19*X19)</f>
+        <v>10000000</v>
+      </c>
+      <c r="AB19" s="41"/>
+      <c r="AC19" s="41"/>
+      <c r="AD19" s="41"/>
+    </row>
+    <row r="20" spans="1:30" ht="150" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="59"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="48">
+        <v>30</v>
+      </c>
+      <c r="U20" s="49"/>
+      <c r="V20" s="50">
+        <v>2</v>
+      </c>
+      <c r="W20" s="51"/>
+      <c r="X20" s="41">
+        <v>5000000</v>
+      </c>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="42"/>
+      <c r="AA20" s="43">
+        <f>SUM(V20*X20)</f>
+        <v>10000000</v>
+      </c>
+      <c r="AB20" s="41"/>
+      <c r="AC20" s="41"/>
+      <c r="AD20" s="41"/>
+    </row>
+    <row r="21" spans="1:30" ht="150" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="59"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="48">
+        <v>30</v>
+      </c>
+      <c r="U21" s="49"/>
+      <c r="V21" s="50">
+        <v>2</v>
+      </c>
+      <c r="W21" s="51"/>
+      <c r="X21" s="41">
+        <v>5000000</v>
+      </c>
+      <c r="Y21" s="41"/>
+      <c r="Z21" s="42"/>
+      <c r="AA21" s="43">
+        <f>SUM(V21*X21)</f>
+        <v>10000000</v>
+      </c>
+      <c r="AB21" s="41"/>
+      <c r="AC21" s="41"/>
+      <c r="AD21" s="41"/>
+    </row>
+    <row r="22" spans="1:30" ht="150" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="61"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="46"/>
+      <c r="O22" s="46"/>
+      <c r="P22" s="46"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="48">
+        <v>30</v>
+      </c>
+      <c r="U22" s="49"/>
+      <c r="V22" s="50">
+        <v>3</v>
+      </c>
+      <c r="W22" s="51"/>
+      <c r="X22" s="41">
+        <v>5000000</v>
+      </c>
+      <c r="Y22" s="41"/>
+      <c r="Z22" s="42"/>
+      <c r="AA22" s="43">
+        <f>SUM(V22*X22)</f>
+        <v>15000000</v>
+      </c>
+      <c r="AB22" s="41"/>
+      <c r="AC22" s="41"/>
+      <c r="AD22" s="41"/>
+    </row>
+    <row r="23" spans="1:30" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="53">
+        <f>SUM(T23*0.1)</f>
+        <v>5000000</v>
+      </c>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="55">
+        <f>SUM(AA13:AD22)</f>
+        <v>50000000</v>
+      </c>
+      <c r="U23" s="56"/>
+      <c r="V23" s="56"/>
+      <c r="W23" s="56"/>
+      <c r="X23" s="56"/>
+      <c r="Y23" s="56"/>
+      <c r="Z23" s="56"/>
+      <c r="AA23" s="56"/>
+      <c r="AB23" s="56"/>
+      <c r="AC23" s="56"/>
+      <c r="AD23" s="56"/>
+    </row>
+    <row r="24" spans="1:30" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="36" t="str">
-        <f>IF(E19="국민은행 [A]", "830501-04-224154", IF(E19="국민은행 [B]", "97112978846", IF(E19="우리은행", "1005-104-299487", IF(E19="기업은행", "052-111285-04-020", IF(E19="신한은행", "140-013-733156", "X")))))</f>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="36" t="str">
+        <f>IF(E24="국민은행 [A]", "830501-04-224154", IF(E24="국민은행 [B]", "97112978846", IF(E24="우리은행", "1005-104-299487", IF(E24="기업은행", "052-111285-04-020", IF(E24="신한은행", "140-013-733156", "X")))))</f>
         <v>97112978846</v>
       </c>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
-      <c r="S19" s="36"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="35" t="s">
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="33" t="s">
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="Z19" s="34"/>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="34"/>
-      <c r="AC19" s="34"/>
-      <c r="AD19" s="34"/>
-    </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="37"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
-      <c r="S20" s="37"/>
-      <c r="T20" s="37"/>
-      <c r="U20" s="37"/>
-      <c r="V20" s="37"/>
-      <c r="W20" s="37"/>
-      <c r="X20" s="37"/>
-      <c r="Y20" s="37"/>
-      <c r="Z20" s="37"/>
-      <c r="AA20" s="37"/>
-      <c r="AB20" s="37"/>
-      <c r="AC20" s="37"/>
-      <c r="AD20" s="37"/>
-    </row>
-    <row r="21" spans="1:30" ht="25.05" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="28" t="s">
+      <c r="Z24" s="34"/>
+      <c r="AA24" s="34"/>
+      <c r="AB24" s="34"/>
+      <c r="AC24" s="34"/>
+      <c r="AD24" s="34"/>
+    </row>
+    <row r="25" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="37"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
+      <c r="S25" s="37"/>
+      <c r="T25" s="37"/>
+      <c r="U25" s="37"/>
+      <c r="V25" s="37"/>
+      <c r="W25" s="37"/>
+      <c r="X25" s="37"/>
+      <c r="Y25" s="37"/>
+      <c r="Z25" s="37"/>
+      <c r="AA25" s="37"/>
+      <c r="AB25" s="37"/>
+      <c r="AC25" s="37"/>
+      <c r="AD25" s="37"/>
+    </row>
+    <row r="26" spans="1:30" ht="25.05" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B26" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="38"/>
-      <c r="X21" s="38"/>
-      <c r="Y21" s="38"/>
-      <c r="Z21" s="38"/>
-      <c r="AA21" s="38"/>
-      <c r="AB21" s="38"/>
-      <c r="AC21" s="38"/>
-      <c r="AD21" s="39"/>
-    </row>
-    <row r="22" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="32"/>
-      <c r="B22" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="24"/>
-      <c r="AA22" s="24"/>
-      <c r="AB22" s="24"/>
-      <c r="AC22" s="24"/>
-      <c r="AD22" s="25"/>
-    </row>
-    <row r="23" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="32"/>
-      <c r="B23" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="24"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="24"/>
-      <c r="AA23" s="24"/>
-      <c r="AB23" s="24"/>
-      <c r="AC23" s="24"/>
-      <c r="AD23" s="25"/>
-    </row>
-    <row r="24" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="32"/>
-      <c r="B24" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="24"/>
-      <c r="U24" s="24"/>
-      <c r="V24" s="24"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="24"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="24"/>
-      <c r="AA24" s="24"/>
-      <c r="AB24" s="24"/>
-      <c r="AC24" s="24"/>
-      <c r="AD24" s="25"/>
-    </row>
-    <row r="25" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="32"/>
-      <c r="B25" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
-      <c r="S25" s="24"/>
-      <c r="T25" s="24"/>
-      <c r="U25" s="24"/>
-      <c r="V25" s="24"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="24"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="24"/>
-      <c r="AC25" s="24"/>
-      <c r="AD25" s="25"/>
-    </row>
-    <row r="26" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="32"/>
-      <c r="B26" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="40"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="40"/>
-      <c r="U26" s="40"/>
-      <c r="V26" s="40"/>
-      <c r="W26" s="40"/>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="40"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="40"/>
-      <c r="AD26" s="40"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="38"/>
+      <c r="Z26" s="38"/>
+      <c r="AA26" s="38"/>
+      <c r="AB26" s="38"/>
+      <c r="AC26" s="38"/>
+      <c r="AD26" s="39"/>
     </row>
     <row r="27" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="32"/>
       <c r="B27" s="24" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C27" s="24"/>
       <c r="D27" s="24"/>
@@ -11246,7 +11305,7 @@
     <row r="28" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="32"/>
       <c r="B28" s="24" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="24"/>
@@ -11280,7 +11339,7 @@
     <row r="29" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="32"/>
       <c r="B29" s="24" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C29" s="24"/>
       <c r="D29" s="24"/>
@@ -11314,7 +11373,7 @@
     <row r="30" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="32"/>
       <c r="B30" s="24" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
@@ -11345,78 +11404,78 @@
       <c r="AC30" s="24"/>
       <c r="AD30" s="25"/>
     </row>
-    <row r="31" spans="1:30" s="5" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="26"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="26"/>
-      <c r="AC31" s="26"/>
-      <c r="AD31" s="26"/>
-    </row>
-    <row r="32" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="30"/>
-    </row>
-    <row r="33" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="27"/>
+    <row r="31" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="32"/>
+      <c r="B31" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="40"/>
+      <c r="S31" s="40"/>
+      <c r="T31" s="40"/>
+      <c r="U31" s="40"/>
+      <c r="V31" s="40"/>
+      <c r="W31" s="40"/>
+      <c r="X31" s="40"/>
+      <c r="Y31" s="40"/>
+      <c r="Z31" s="40"/>
+      <c r="AA31" s="40"/>
+      <c r="AB31" s="40"/>
+      <c r="AC31" s="40"/>
+      <c r="AD31" s="40"/>
+    </row>
+    <row r="32" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="32"/>
+      <c r="B32" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
+      <c r="Q32" s="24"/>
+      <c r="R32" s="24"/>
+      <c r="S32" s="24"/>
+      <c r="T32" s="24"/>
+      <c r="U32" s="24"/>
+      <c r="V32" s="24"/>
+      <c r="W32" s="24"/>
+      <c r="X32" s="24"/>
+      <c r="Y32" s="24"/>
+      <c r="Z32" s="24"/>
+      <c r="AA32" s="24"/>
+      <c r="AB32" s="24"/>
+      <c r="AC32" s="24"/>
+      <c r="AD32" s="25"/>
+    </row>
+    <row r="33" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="32"/>
       <c r="B33" s="24" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
@@ -11447,10 +11506,10 @@
       <c r="AC33" s="24"/>
       <c r="AD33" s="25"/>
     </row>
-    <row r="34" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="27"/>
+    <row r="34" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="32"/>
       <c r="B34" s="24" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C34" s="24"/>
       <c r="D34" s="24"/>
@@ -11481,10 +11540,10 @@
       <c r="AC34" s="24"/>
       <c r="AD34" s="25"/>
     </row>
-    <row r="35" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="27"/>
+    <row r="35" spans="1:30" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="32"/>
       <c r="B35" s="24" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
@@ -11515,451 +11574,653 @@
       <c r="AC35" s="24"/>
       <c r="AD35" s="25"/>
     </row>
-    <row r="36" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="27"/>
-      <c r="B36" s="24" t="s">
+    <row r="36" spans="1:30" s="5" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="26"/>
+      <c r="U36" s="26"/>
+      <c r="V36" s="26"/>
+      <c r="W36" s="26"/>
+      <c r="X36" s="26"/>
+      <c r="Y36" s="26"/>
+      <c r="Z36" s="26"/>
+      <c r="AA36" s="26"/>
+      <c r="AB36" s="26"/>
+      <c r="AC36" s="26"/>
+      <c r="AD36" s="26"/>
+    </row>
+    <row r="37" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29"/>
+      <c r="Y37" s="29"/>
+      <c r="Z37" s="29"/>
+      <c r="AA37" s="29"/>
+      <c r="AB37" s="29"/>
+      <c r="AC37" s="29"/>
+      <c r="AD37" s="30"/>
+    </row>
+    <row r="38" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="27"/>
+      <c r="B38" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="24"/>
+      <c r="S38" s="24"/>
+      <c r="T38" s="24"/>
+      <c r="U38" s="24"/>
+      <c r="V38" s="24"/>
+      <c r="W38" s="24"/>
+      <c r="X38" s="24"/>
+      <c r="Y38" s="24"/>
+      <c r="Z38" s="24"/>
+      <c r="AA38" s="24"/>
+      <c r="AB38" s="24"/>
+      <c r="AC38" s="24"/>
+      <c r="AD38" s="25"/>
+    </row>
+    <row r="39" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="27"/>
+      <c r="B39" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="24"/>
+      <c r="R39" s="24"/>
+      <c r="S39" s="24"/>
+      <c r="T39" s="24"/>
+      <c r="U39" s="24"/>
+      <c r="V39" s="24"/>
+      <c r="W39" s="24"/>
+      <c r="X39" s="24"/>
+      <c r="Y39" s="24"/>
+      <c r="Z39" s="24"/>
+      <c r="AA39" s="24"/>
+      <c r="AB39" s="24"/>
+      <c r="AC39" s="24"/>
+      <c r="AD39" s="25"/>
+    </row>
+    <row r="40" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="27"/>
+      <c r="B40" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="24"/>
+      <c r="S40" s="24"/>
+      <c r="T40" s="24"/>
+      <c r="U40" s="24"/>
+      <c r="V40" s="24"/>
+      <c r="W40" s="24"/>
+      <c r="X40" s="24"/>
+      <c r="Y40" s="24"/>
+      <c r="Z40" s="24"/>
+      <c r="AA40" s="24"/>
+      <c r="AB40" s="24"/>
+      <c r="AC40" s="24"/>
+      <c r="AD40" s="25"/>
+    </row>
+    <row r="41" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="27"/>
+      <c r="B41" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="24"/>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="24"/>
-      <c r="Y36" s="24"/>
-      <c r="Z36" s="24"/>
-      <c r="AA36" s="24"/>
-      <c r="AB36" s="24"/>
-      <c r="AC36" s="24"/>
-      <c r="AD36" s="25"/>
-    </row>
-    <row r="37" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="28"/>
-      <c r="B37" s="24" t="s">
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="24"/>
+      <c r="Q41" s="24"/>
+      <c r="R41" s="24"/>
+      <c r="S41" s="24"/>
+      <c r="T41" s="24"/>
+      <c r="U41" s="24"/>
+      <c r="V41" s="24"/>
+      <c r="W41" s="24"/>
+      <c r="X41" s="24"/>
+      <c r="Y41" s="24"/>
+      <c r="Z41" s="24"/>
+      <c r="AA41" s="24"/>
+      <c r="AB41" s="24"/>
+      <c r="AC41" s="24"/>
+      <c r="AD41" s="25"/>
+    </row>
+    <row r="42" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="28"/>
+      <c r="B42" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
-      <c r="R37" s="24"/>
-      <c r="S37" s="24"/>
-      <c r="T37" s="24"/>
-      <c r="U37" s="24"/>
-      <c r="V37" s="24"/>
-      <c r="W37" s="24"/>
-      <c r="X37" s="24"/>
-      <c r="Y37" s="24"/>
-      <c r="Z37" s="24"/>
-      <c r="AA37" s="24"/>
-      <c r="AB37" s="24"/>
-      <c r="AC37" s="24"/>
-      <c r="AD37" s="25"/>
-    </row>
-    <row r="38" spans="1:30" s="5" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="4"/>
-      <c r="AC38" s="4"/>
-      <c r="AD38" s="4"/>
-    </row>
-    <row r="39" spans="1:30" s="5" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="18" t="s">
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
+      <c r="R42" s="24"/>
+      <c r="S42" s="24"/>
+      <c r="T42" s="24"/>
+      <c r="U42" s="24"/>
+      <c r="V42" s="24"/>
+      <c r="W42" s="24"/>
+      <c r="X42" s="24"/>
+      <c r="Y42" s="24"/>
+      <c r="Z42" s="24"/>
+      <c r="AA42" s="24"/>
+      <c r="AB42" s="24"/>
+      <c r="AC42" s="24"/>
+      <c r="AD42" s="25"/>
+    </row>
+    <row r="43" spans="1:30" s="5" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="4"/>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+    </row>
+    <row r="44" spans="1:30" s="5" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="18"/>
-      <c r="V39" s="18"/>
-      <c r="W39" s="18"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="18"/>
-      <c r="Z39" s="18"/>
-      <c r="AA39" s="18"/>
-      <c r="AB39" s="18"/>
-      <c r="AC39" s="18"/>
-      <c r="AD39" s="18"/>
-    </row>
-    <row r="40" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="19" t="s">
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="18"/>
+      <c r="X44" s="18"/>
+      <c r="Y44" s="18"/>
+      <c r="Z44" s="18"/>
+      <c r="AA44" s="18"/>
+      <c r="AB44" s="18"/>
+      <c r="AC44" s="18"/>
+      <c r="AD44" s="18"/>
+    </row>
+    <row r="45" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="21" t="s">
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="22" t="s">
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="23"/>
+      <c r="K45" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="L40" s="22"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="22"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="22" t="s">
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="23"/>
+      <c r="P45" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="Q40" s="22"/>
-      <c r="R40" s="22"/>
-      <c r="S40" s="22"/>
-      <c r="T40" s="23"/>
-      <c r="U40" s="21" t="s">
+      <c r="Q45" s="22"/>
+      <c r="R45" s="22"/>
+      <c r="S45" s="22"/>
+      <c r="T45" s="23"/>
+      <c r="U45" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="V40" s="22"/>
-      <c r="W40" s="22"/>
-      <c r="X40" s="22"/>
-      <c r="Y40" s="23"/>
-      <c r="Z40" s="19" t="s">
+      <c r="V45" s="22"/>
+      <c r="W45" s="22"/>
+      <c r="X45" s="22"/>
+      <c r="Y45" s="23"/>
+      <c r="Z45" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AA40" s="19"/>
-      <c r="AB40" s="19"/>
-      <c r="AC40" s="19"/>
-      <c r="AD40" s="19"/>
-    </row>
-    <row r="41" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="9" t="s">
+      <c r="AA45" s="19"/>
+      <c r="AB45" s="19"/>
+      <c r="AC45" s="19"/>
+      <c r="AD45" s="19"/>
+    </row>
+    <row r="46" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="12">
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="12">
         <v>463265</v>
       </c>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="11">
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="11">
         <v>9543259</v>
       </c>
-      <c r="L41" s="12"/>
-      <c r="M41" s="12"/>
-      <c r="N41" s="12"/>
-      <c r="O41" s="13"/>
-      <c r="P41" s="11">
-        <f>SUM(K41*1.1)</f>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="11">
+        <f>SUM(K46*1.1)</f>
         <v>10497584.9</v>
       </c>
-      <c r="Q41" s="12"/>
-      <c r="R41" s="12"/>
-      <c r="S41" s="12"/>
-      <c r="T41" s="13"/>
-      <c r="U41" s="11" cm="1">
-        <f t="array" ref="U41">SUM(K41:T41*0.2)</f>
+      <c r="Q46" s="12"/>
+      <c r="R46" s="12"/>
+      <c r="S46" s="12"/>
+      <c r="T46" s="13"/>
+      <c r="U46" s="11" cm="1">
+        <f t="array" ref="U46">SUM(K46:T46*0.2)</f>
         <v>4008168.7800000003</v>
       </c>
-      <c r="V41" s="12"/>
-      <c r="W41" s="12"/>
-      <c r="X41" s="12"/>
-      <c r="Y41" s="13"/>
-      <c r="Z41" s="12">
-        <f>SUM(F41:Y41)</f>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="13"/>
+      <c r="Z46" s="12">
+        <f>SUM(F46:Y46)</f>
         <v>24512277.68</v>
       </c>
-      <c r="AA41" s="12"/>
-      <c r="AB41" s="12"/>
-      <c r="AC41" s="12"/>
-      <c r="AD41" s="12"/>
-    </row>
-    <row r="42" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="16" t="s">
+      <c r="AA46" s="12"/>
+      <c r="AB46" s="12"/>
+      <c r="AC46" s="12"/>
+      <c r="AD46" s="12"/>
+    </row>
+    <row r="47" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="11">
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="11">
         <v>291414</v>
       </c>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="11">
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="11">
         <v>6003128</v>
       </c>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="11">
-        <f>SUM(K42*1.1)</f>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="11">
+        <f>SUM(K47*1.1)</f>
         <v>6603440.8000000007</v>
       </c>
-      <c r="Q42" s="12"/>
-      <c r="R42" s="12"/>
-      <c r="S42" s="12"/>
-      <c r="T42" s="13"/>
-      <c r="U42" s="11" cm="1">
-        <f t="array" ref="U42">SUM(K42:T42*0.2)</f>
+      <c r="Q47" s="12"/>
+      <c r="R47" s="12"/>
+      <c r="S47" s="12"/>
+      <c r="T47" s="13"/>
+      <c r="U47" s="11" cm="1">
+        <f t="array" ref="U47">SUM(K47:T47*0.2)</f>
         <v>2521313.7600000002</v>
       </c>
-      <c r="V42" s="12"/>
-      <c r="W42" s="12"/>
-      <c r="X42" s="12"/>
-      <c r="Y42" s="12"/>
-      <c r="Z42" s="11">
-        <f t="shared" ref="Z42:Z44" si="1">SUM(F42:Y42)</f>
+      <c r="V47" s="12"/>
+      <c r="W47" s="12"/>
+      <c r="X47" s="12"/>
+      <c r="Y47" s="12"/>
+      <c r="Z47" s="11">
+        <f t="shared" ref="Z47:Z49" si="1">SUM(F47:Y47)</f>
         <v>15419296.560000001</v>
       </c>
-      <c r="AA42" s="12"/>
-      <c r="AB42" s="12"/>
-      <c r="AC42" s="12"/>
-      <c r="AD42" s="12"/>
-    </row>
-    <row r="43" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="14" t="s">
+      <c r="AA47" s="12"/>
+      <c r="AB47" s="12"/>
+      <c r="AC47" s="12"/>
+      <c r="AD47" s="12"/>
+    </row>
+    <row r="48" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="11">
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="11">
         <v>291414</v>
       </c>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="11">
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="11">
         <v>6003128</v>
       </c>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="11">
-        <f>SUM(K43*1.1)</f>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="11">
+        <f>SUM(K48*1.1)</f>
         <v>6603440.8000000007</v>
       </c>
-      <c r="Q43" s="12"/>
-      <c r="R43" s="12"/>
-      <c r="S43" s="12"/>
-      <c r="T43" s="13"/>
-      <c r="U43" s="11" cm="1">
-        <f t="array" ref="U43">SUM(K43:T43*0.2)</f>
+      <c r="Q48" s="12"/>
+      <c r="R48" s="12"/>
+      <c r="S48" s="12"/>
+      <c r="T48" s="13"/>
+      <c r="U48" s="11" cm="1">
+        <f t="array" ref="U48">SUM(K48:T48*0.2)</f>
         <v>2521313.7600000002</v>
       </c>
-      <c r="V43" s="12"/>
-      <c r="W43" s="12"/>
-      <c r="X43" s="12"/>
-      <c r="Y43" s="12"/>
-      <c r="Z43" s="11">
+      <c r="V48" s="12"/>
+      <c r="W48" s="12"/>
+      <c r="X48" s="12"/>
+      <c r="Y48" s="12"/>
+      <c r="Z48" s="11">
         <f t="shared" si="1"/>
         <v>15419296.560000001</v>
       </c>
-      <c r="AA43" s="12"/>
-      <c r="AB43" s="12"/>
-      <c r="AC43" s="12"/>
-      <c r="AD43" s="12"/>
-    </row>
-    <row r="44" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="9" t="s">
+      <c r="AA48" s="12"/>
+      <c r="AB48" s="12"/>
+      <c r="AC48" s="12"/>
+      <c r="AD48" s="12"/>
+    </row>
+    <row r="49" spans="1:30" s="5" customFormat="1" ht="25.05" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="11">
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="11">
         <v>217843</v>
       </c>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="11">
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="11">
         <v>4487566</v>
       </c>
-      <c r="L44" s="12"/>
-      <c r="M44" s="12"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="11">
-        <f>SUM(K44*1.1)</f>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="11">
+        <f>SUM(K49*1.1)</f>
         <v>4936322.6000000006</v>
       </c>
-      <c r="Q44" s="12"/>
-      <c r="R44" s="12"/>
-      <c r="S44" s="12"/>
-      <c r="T44" s="13"/>
-      <c r="U44" s="11" cm="1">
-        <f t="array" ref="U44">SUM(K44:T44*0.2)</f>
+      <c r="Q49" s="12"/>
+      <c r="R49" s="12"/>
+      <c r="S49" s="12"/>
+      <c r="T49" s="13"/>
+      <c r="U49" s="11" cm="1">
+        <f t="array" ref="U49">SUM(K49:T49*0.2)</f>
         <v>1884777.7200000002</v>
       </c>
-      <c r="V44" s="12"/>
-      <c r="W44" s="12"/>
-      <c r="X44" s="12"/>
-      <c r="Y44" s="12"/>
-      <c r="Z44" s="11">
+      <c r="V49" s="12"/>
+      <c r="W49" s="12"/>
+      <c r="X49" s="12"/>
+      <c r="Y49" s="12"/>
+      <c r="Z49" s="11">
         <f t="shared" si="1"/>
         <v>11526509.320000002</v>
       </c>
-      <c r="AA44" s="12"/>
-      <c r="AB44" s="12"/>
-      <c r="AC44" s="12"/>
-      <c r="AD44" s="12"/>
-    </row>
-    <row r="45" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="AA45" s="6"/>
-    </row>
-    <row r="46" spans="1:30" ht="2.5499999999999998" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="2"/>
-      <c r="X46" s="2"/>
-      <c r="Y46" s="2"/>
-      <c r="Z46" s="2"/>
-      <c r="AA46" s="2"/>
-      <c r="AB46" s="2"/>
-      <c r="AC46" s="2"/>
-      <c r="AD46" s="2"/>
-    </row>
-    <row r="47" spans="1:30" ht="100.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="7" t="s">
+      <c r="AA49" s="12"/>
+      <c r="AB49" s="12"/>
+      <c r="AC49" s="12"/>
+      <c r="AD49" s="12"/>
+    </row>
+    <row r="50" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="AA50" s="6"/>
+    </row>
+    <row r="51" spans="1:30" ht="2.5499999999999998" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
+      <c r="T51" s="2"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="2"/>
+      <c r="W51" s="2"/>
+      <c r="X51" s="2"/>
+      <c r="Y51" s="2"/>
+      <c r="Z51" s="2"/>
+      <c r="AA51" s="2"/>
+      <c r="AB51" s="2"/>
+      <c r="AC51" s="2"/>
+      <c r="AD51" s="2"/>
+    </row>
+    <row r="52" spans="1:30" ht="100.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8"/>
-      <c r="Q47" s="8"/>
-      <c r="R47" s="8"/>
-      <c r="S47" s="8"/>
-      <c r="T47" s="8"/>
-      <c r="U47" s="8"/>
-      <c r="V47" s="8"/>
-      <c r="W47" s="8"/>
-      <c r="X47" s="8"/>
-      <c r="Y47" s="8"/>
-      <c r="Z47" s="8"/>
-      <c r="AA47" s="8"/>
-      <c r="AB47" s="8"/>
-      <c r="AC47" s="8"/>
-      <c r="AD47" s="8"/>
-    </row>
-    <row r="48" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="49" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="50" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="51" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="Q52" s="8"/>
+      <c r="R52" s="8"/>
+      <c r="S52" s="8"/>
+      <c r="T52" s="8"/>
+      <c r="U52" s="8"/>
+      <c r="V52" s="8"/>
+      <c r="W52" s="8"/>
+      <c r="X52" s="8"/>
+      <c r="Y52" s="8"/>
+      <c r="Z52" s="8"/>
+      <c r="AA52" s="8"/>
+      <c r="AB52" s="8"/>
+      <c r="AC52" s="8"/>
+      <c r="AD52" s="8"/>
+    </row>
+    <row r="53" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="54" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="55" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="56" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="57" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="58" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" ht="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="135">
+  <mergeCells count="167">
+    <mergeCell ref="I21:S21"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="AA19:AD19"/>
+    <mergeCell ref="X20:Z20"/>
+    <mergeCell ref="AA20:AD20"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="AA21:AD21"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="AA22:AD22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="X18:Z18"/>
+    <mergeCell ref="X22:Z22"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="AA18:AD18"/>
+    <mergeCell ref="A18:B22"/>
+    <mergeCell ref="C18:D22"/>
+    <mergeCell ref="I18:S18"/>
+    <mergeCell ref="I22:S22"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I19:S19"/>
+    <mergeCell ref="I20:S20"/>
     <mergeCell ref="I16:S16"/>
     <mergeCell ref="T14:U14"/>
     <mergeCell ref="T15:U15"/>
@@ -12009,10 +12270,10 @@
     <mergeCell ref="D7:O7"/>
     <mergeCell ref="D8:O8"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="T18:AD18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="T23:AD23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="P23:S23"/>
     <mergeCell ref="T17:U17"/>
     <mergeCell ref="AA17:AD17"/>
     <mergeCell ref="T13:U13"/>
@@ -12032,69 +12293,69 @@
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="I14:S14"/>
     <mergeCell ref="I15:S15"/>
-    <mergeCell ref="E19:J19"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="Y19:AD19"/>
-    <mergeCell ref="B27:AD27"/>
-    <mergeCell ref="B28:AD28"/>
-    <mergeCell ref="A47:AD47"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="O24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AD24"/>
+    <mergeCell ref="B32:AD32"/>
+    <mergeCell ref="B33:AD33"/>
+    <mergeCell ref="A52:AD52"/>
     <mergeCell ref="AB3:AD3"/>
     <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="A20:AD20"/>
+    <mergeCell ref="A25:AD25"/>
     <mergeCell ref="S5:Y5"/>
     <mergeCell ref="Z5:AA5"/>
     <mergeCell ref="AB5:AD5"/>
-    <mergeCell ref="A21:A30"/>
-    <mergeCell ref="B21:AD21"/>
-    <mergeCell ref="B22:AD22"/>
-    <mergeCell ref="B23:AD23"/>
-    <mergeCell ref="B24:AD24"/>
-    <mergeCell ref="B25:AD25"/>
+    <mergeCell ref="A26:A35"/>
     <mergeCell ref="B26:AD26"/>
+    <mergeCell ref="B27:AD27"/>
+    <mergeCell ref="B28:AD28"/>
     <mergeCell ref="B29:AD29"/>
     <mergeCell ref="B30:AD30"/>
-    <mergeCell ref="E18:O18"/>
-    <mergeCell ref="Z40:AD40"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="F41:J41"/>
-    <mergeCell ref="K41:O41"/>
-    <mergeCell ref="P41:T41"/>
-    <mergeCell ref="U41:Y41"/>
-    <mergeCell ref="Z41:AD41"/>
-    <mergeCell ref="A31:AD31"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="B32:AD32"/>
-    <mergeCell ref="B33:AD33"/>
+    <mergeCell ref="B31:AD31"/>
     <mergeCell ref="B34:AD34"/>
     <mergeCell ref="B35:AD35"/>
-    <mergeCell ref="B36:AD36"/>
+    <mergeCell ref="E23:O23"/>
+    <mergeCell ref="Z45:AD45"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="F46:J46"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="P46:T46"/>
+    <mergeCell ref="U46:Y46"/>
+    <mergeCell ref="Z46:AD46"/>
+    <mergeCell ref="A36:AD36"/>
+    <mergeCell ref="A37:A42"/>
     <mergeCell ref="B37:AD37"/>
-    <mergeCell ref="A39:AD39"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="F40:J40"/>
-    <mergeCell ref="K40:O40"/>
-    <mergeCell ref="P40:T40"/>
-    <mergeCell ref="U40:Y40"/>
-    <mergeCell ref="Z42:AD42"/>
-    <mergeCell ref="Z43:AD43"/>
-    <mergeCell ref="Z44:AD44"/>
-    <mergeCell ref="P42:T42"/>
-    <mergeCell ref="P43:T43"/>
-    <mergeCell ref="P44:T44"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="K43:O43"/>
-    <mergeCell ref="K44:O44"/>
-    <mergeCell ref="F42:J42"/>
-    <mergeCell ref="F43:J43"/>
-    <mergeCell ref="F44:J44"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="U42:Y42"/>
-    <mergeCell ref="U43:Y43"/>
-    <mergeCell ref="U44:Y44"/>
+    <mergeCell ref="B38:AD38"/>
+    <mergeCell ref="B39:AD39"/>
+    <mergeCell ref="B40:AD40"/>
+    <mergeCell ref="B41:AD41"/>
+    <mergeCell ref="B42:AD42"/>
+    <mergeCell ref="A44:AD44"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="F45:J45"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="P45:T45"/>
+    <mergeCell ref="U45:Y45"/>
+    <mergeCell ref="Z47:AD47"/>
+    <mergeCell ref="Z48:AD48"/>
+    <mergeCell ref="Z49:AD49"/>
+    <mergeCell ref="P47:T47"/>
+    <mergeCell ref="P48:T48"/>
+    <mergeCell ref="P49:T49"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="K49:O49"/>
+    <mergeCell ref="F47:J47"/>
+    <mergeCell ref="F48:J48"/>
+    <mergeCell ref="F49:J49"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="U47:Y47"/>
+    <mergeCell ref="U48:Y48"/>
+    <mergeCell ref="U49:Y49"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/backend/templates/alphabrothers.xlsx
+++ b/backend/templates/alphabrothers.xlsx
@@ -2084,8 +2084,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9677401" y="2124076"/>
-          <a:ext cx="609600" cy="609600"/>
+          <a:off x="12338051" y="2139951"/>
+          <a:ext cx="615950" cy="622300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
